--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\ck-tools-main\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3524334-D887-433D-8335-CA14EE1DC1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:1_{E3524334-D887-433D-8335-CA14EE1DC1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5693C9C2-B264-4E5B-A3D3-829BA115DB25}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="4395" yWindow="2085" windowWidth="21600" windowHeight="11295" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3571" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3685" uniqueCount="261">
   <si>
     <t>Team 1</t>
   </si>
@@ -893,7 +893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -924,6 +924,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -942,7 +951,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1258,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:I595"/>
+  <dimension ref="A1:I614"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
@@ -15018,6 +15027,443 @@
         <v>46247</v>
       </c>
     </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A596" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C596" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D596" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E596" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F596" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G596" s="6">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A597" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C597" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D597" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E597" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F597" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G597" s="6">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A598" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B598" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C598" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D598" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E598" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F598" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G598" s="5">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A599" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B599" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C599" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D599" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E599" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F599" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G599" s="5">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A600" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B600" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C600" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D600" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E600" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F600" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G600" s="5">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A601" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C601" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D601" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E601" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F601" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G601" s="6">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A602" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C602" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D602" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E602" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F602" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G602" s="6">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A603" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B603" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C603" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D603" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E603" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F603" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G603" s="5">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A604" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B604" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C604" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D604" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E604" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F604" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G604" s="5">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A605" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C605" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D605" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E605" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F605" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G605" s="6">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A606" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D606" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E606" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F606" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G606" s="6">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A607" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B607" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C607" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D607" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E607" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F607" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G607" s="5">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A608" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B608" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C608" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D608" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E608" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F608" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G608" s="5">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A609" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B609" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C609" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D609" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E609" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F609" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="G609" s="14">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A610" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B610" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C610" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D610" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E610" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F610" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="G610" s="14">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A611" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B611" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C611" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D611" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E611" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F611" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G611" s="5">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A612" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B612" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C612" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D612" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E612" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F612" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G612" s="5">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A613" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B613" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C613" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D613" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E613" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F613" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G613" s="5">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A614" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B614" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C614" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D614" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E614" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F614" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G614" s="5">
+        <v>46253</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:1_{E3524334-D887-433D-8335-CA14EE1DC1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5693C9C2-B264-4E5B-A3D3-829BA115DB25}"/>
+  <xr:revisionPtr revIDLastSave="425" documentId="13_ncr:1_{E3524334-D887-433D-8335-CA14EE1DC1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63C5589D-20FD-43B8-B7B1-532B941C8F46}"/>
   <bookViews>
     <workbookView xWindow="4395" yWindow="2085" windowWidth="21600" windowHeight="11295" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3685" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3895" uniqueCount="270">
   <si>
     <t>Team 1</t>
   </si>
@@ -819,6 +819,33 @@
   </si>
   <si>
     <t>ASIA OQ</t>
+  </si>
+  <si>
+    <t>Bravado</t>
+  </si>
+  <si>
+    <t>Rogue</t>
+  </si>
+  <si>
+    <t>GATERON</t>
+  </si>
+  <si>
+    <t>kONO</t>
+  </si>
+  <si>
+    <t>FORZE</t>
+  </si>
+  <si>
+    <t>LGB</t>
+  </si>
+  <si>
+    <t>Shika</t>
+  </si>
+  <si>
+    <t>Avangar</t>
+  </si>
+  <si>
+    <t>Fragadelphia 2026</t>
   </si>
 </sst>
 </file>
@@ -893,7 +920,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -924,15 +951,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -948,6 +966,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1267,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:I614"/>
+  <dimension ref="A1:I649"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
@@ -15178,7 +15200,7 @@
       <c r="D602" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E602" s="13" t="s">
+      <c r="E602" s="8" t="s">
         <v>210</v>
       </c>
       <c r="F602" s="1" t="s">
@@ -15270,7 +15292,7 @@
       <c r="D606" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E606" s="13" t="s">
+      <c r="E606" s="8" t="s">
         <v>210</v>
       </c>
       <c r="F606" s="1" t="s">
@@ -15327,48 +15349,48 @@
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A609" s="12" t="s">
+      <c r="A609" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B609" s="12" t="s">
+      <c r="B609" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C609" s="12" t="s">
+      <c r="C609" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D609" s="12" t="s">
+      <c r="D609" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E609" s="13" t="s">
+      <c r="E609" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="F609" s="12" t="s">
+      <c r="F609" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G609" s="14">
+      <c r="G609" s="6">
         <v>46253</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A610" s="12" t="s">
+      <c r="A610" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B610" s="12" t="s">
+      <c r="B610" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C610" s="12" t="s">
+      <c r="C610" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D610" s="12" t="s">
+      <c r="D610" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E610" s="13" t="s">
+      <c r="E610" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="F610" s="12" t="s">
+      <c r="F610" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G610" s="14">
+      <c r="G610" s="6">
         <v>46253</v>
       </c>
     </row>
@@ -15462,6 +15484,811 @@
       </c>
       <c r="G614" s="5">
         <v>46253</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A615" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C615" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D615" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E615" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F615" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G615" s="6">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A616" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D616" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E616" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F616" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G616" s="6">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A617" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B617" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C617" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D617" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E617" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F617" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G617" s="5">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A618" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B618" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C618" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D618" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E618" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F618" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G618" s="5">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A619" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C619" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D619" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E619" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F619" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G619" s="6">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A620" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C620" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D620" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E620" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F620" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G620" s="6">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A621" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B621" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C621" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D621" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E621" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F621" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G621" s="5">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A622" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B622" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D622" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E622" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F622" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G622" s="5">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A623" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C623" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D623" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E623" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F623" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G623" s="6">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A624" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C624" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D624" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E624" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F624" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G624" s="6">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A625" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B625" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C625" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D625" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E625" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F625" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G625" s="5">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A626" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B626" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D626" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E626" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F626" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G626" s="5">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A627" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C627" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D627" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E627" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F627" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G627" s="6">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A628" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C628" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D628" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E628" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F628" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G628" s="6">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A629" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C629" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D629" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E629" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F629" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G629" s="6">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A630" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B630" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C630" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D630" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E630" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F630" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G630" s="5">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A631" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B631" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D631" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E631" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F631" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G631" s="5">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A632" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C632" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D632" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E632" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F632" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G632" s="6">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A633" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C633" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D633" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E633" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F633" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G633" s="6">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A634" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C634" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D634" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F634" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G634" s="6">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A635" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B635" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C635" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D635" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E635" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F635" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G635" s="5">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A636" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D636" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E636" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F636" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G636" s="5">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A637" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B637" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D637" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E637" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F637" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G637" s="5">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A638" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C638" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D638" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E638" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F638" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G638" s="6">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A639" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C639" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D639" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E639" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F639" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G639" s="6">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A640" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B640" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D640" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E640" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F640" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G640" s="5">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A641" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B641" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C641" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D641" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E641" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F641" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G641" s="5">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A642" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B642" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D642" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E642" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F642" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G642" s="5">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A643" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C643" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D643" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E643" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F643" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G643" s="6">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="644" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A644" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C644" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D644" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E644" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F644" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G644" s="6">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A645" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B645" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C645" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D645" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E645" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F645" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G645" s="5">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="646" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A646" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B646" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D646" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E646" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F646" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G646" s="5">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A647" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B647" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D647" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E647" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F647" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G647" s="5">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="648" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A648" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B648" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D648" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E648" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F648" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G648" s="5">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="649" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A649" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B649" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D649" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E649" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F649" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G649" s="5">
+        <v>46258</v>
       </c>
     </row>
   </sheetData>
